--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/27.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/27.xlsx
@@ -426,13 +426,13 @@
         <v>-14.6585519992941</v>
       </c>
       <c r="E2">
-        <v>-7.500083370581287</v>
+        <v>-7.763658671723732</v>
       </c>
       <c r="F2">
-        <v>0.7088827516334794</v>
+        <v>-0.3834815709527103</v>
       </c>
       <c r="G2">
-        <v>-14.92052395870632</v>
+        <v>-14.01945636328195</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.37443943585887</v>
       </c>
       <c r="E3">
-        <v>-8.392111237560208</v>
+        <v>-7.271341091505842</v>
       </c>
       <c r="F3">
-        <v>0.8637802761048654</v>
+        <v>-0.3448431058807764</v>
       </c>
       <c r="G3">
-        <v>-15.0875492575264</v>
+        <v>-13.3306907427455</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.0412534895918</v>
       </c>
       <c r="E4">
-        <v>-9.032908423541596</v>
+        <v>-7.25542350536888</v>
       </c>
       <c r="F4">
-        <v>0.5798899048209364</v>
+        <v>-0.4719465915362002</v>
       </c>
       <c r="G4">
-        <v>-14.08335485800819</v>
+        <v>-13.06646948216519</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.6665309556122</v>
       </c>
       <c r="E5">
-        <v>-9.283713427982409</v>
+        <v>-8.28720008022451</v>
       </c>
       <c r="F5">
-        <v>0.7996243494704134</v>
+        <v>-0.1196084505869782</v>
       </c>
       <c r="G5">
-        <v>-12.56360423584097</v>
+        <v>-13.20287720056531</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.24211496994137</v>
       </c>
       <c r="E6">
-        <v>-11.2113761296715</v>
+        <v>-10.41195555614943</v>
       </c>
       <c r="F6">
-        <v>1.519643574277635</v>
+        <v>0.183337862124476</v>
       </c>
       <c r="G6">
-        <v>-12.50266040300853</v>
+        <v>-12.24181589887827</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.77094404381703</v>
       </c>
       <c r="E7">
-        <v>-11.55908142092844</v>
+        <v>-9.745278141214211</v>
       </c>
       <c r="F7">
-        <v>1.18901012289951</v>
+        <v>-0.1852506852230701</v>
       </c>
       <c r="G7">
-        <v>-12.41039549882904</v>
+        <v>-11.98000802599609</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.25941200309456</v>
       </c>
       <c r="E8">
-        <v>-12.32317989719068</v>
+        <v>-11.48161281607923</v>
       </c>
       <c r="F8">
-        <v>1.270743601489425</v>
+        <v>0.4829180079126636</v>
       </c>
       <c r="G8">
-        <v>-11.98016693218197</v>
+        <v>-11.7830007714996</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.72852499029989</v>
       </c>
       <c r="E9">
-        <v>-12.43839333289383</v>
+        <v>-12.58092252381124</v>
       </c>
       <c r="F9">
-        <v>1.545760468529147</v>
+        <v>0.6173920608985425</v>
       </c>
       <c r="G9">
-        <v>-11.15481813433181</v>
+        <v>-11.6052046127675</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.19451068207033</v>
       </c>
       <c r="E10">
-        <v>-13.98003079627306</v>
+        <v>-13.56706113761757</v>
       </c>
       <c r="F10">
-        <v>1.260267386858793</v>
+        <v>-0.09379958713601924</v>
       </c>
       <c r="G10">
-        <v>-10.98036231604884</v>
+        <v>-10.38628491902663</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.68079085718923</v>
       </c>
       <c r="E11">
-        <v>-14.46378050366844</v>
+        <v>-13.46572747474793</v>
       </c>
       <c r="F11">
-        <v>1.65487938980884</v>
+        <v>0.4792176790412394</v>
       </c>
       <c r="G11">
-        <v>-9.992505458766935</v>
+        <v>-9.911228255232288</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.20325547068351</v>
       </c>
       <c r="E12">
-        <v>-14.93236435161213</v>
+        <v>-14.21067956290574</v>
       </c>
       <c r="F12">
-        <v>1.574327355831843</v>
+        <v>0.6980042757003259</v>
       </c>
       <c r="G12">
-        <v>-9.721818702748427</v>
+        <v>-9.229785561428708</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.762846110849381</v>
       </c>
       <c r="E13">
-        <v>-16.70296598929319</v>
+        <v>-14.83545500784798</v>
       </c>
       <c r="F13">
-        <v>1.614810046442307</v>
+        <v>0.7492593339476081</v>
       </c>
       <c r="G13">
-        <v>-7.89094797661881</v>
+        <v>-8.815123179907294</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.359927470779617</v>
       </c>
       <c r="E14">
-        <v>-17.27375749559</v>
+        <v>-16.49330217121206</v>
       </c>
       <c r="F14">
-        <v>1.891800211052666</v>
+        <v>0.7821354850462157</v>
       </c>
       <c r="G14">
-        <v>-7.929704533247058</v>
+        <v>-7.969894556093811</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.977255527167138</v>
       </c>
       <c r="E15">
-        <v>-18.05770880190186</v>
+        <v>-16.94446497964824</v>
       </c>
       <c r="F15">
-        <v>1.981238418921193</v>
+        <v>1.04444152840862</v>
       </c>
       <c r="G15">
-        <v>-7.173834154629582</v>
+        <v>-7.237092058793976</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.591010575054128</v>
       </c>
       <c r="E16">
-        <v>-19.26080207694167</v>
+        <v>-19.58728241052466</v>
       </c>
       <c r="F16">
-        <v>2.216554946072679</v>
+        <v>1.351176857522763</v>
       </c>
       <c r="G16">
-        <v>-6.388827664720981</v>
+        <v>-6.138113429940895</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.18832028254911</v>
       </c>
       <c r="E17">
-        <v>-19.70412156839656</v>
+        <v>-18.47720852007641</v>
       </c>
       <c r="F17">
-        <v>2.202428289306959</v>
+        <v>1.101163539476</v>
       </c>
       <c r="G17">
-        <v>-5.807505799661578</v>
+        <v>-5.166325960706613</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.756330104557983</v>
       </c>
       <c r="E18">
-        <v>-21.34136870349974</v>
+        <v>-20.39012651039652</v>
       </c>
       <c r="F18">
-        <v>2.930464233458135</v>
+        <v>1.50582415645951</v>
       </c>
       <c r="G18">
-        <v>-4.73599145660229</v>
+        <v>-5.118710384215276</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.291832280961884</v>
       </c>
       <c r="E19">
-        <v>-22.04233572362104</v>
+        <v>-20.16008455928088</v>
       </c>
       <c r="F19">
-        <v>2.677804542826672</v>
+        <v>1.619537408599893</v>
       </c>
       <c r="G19">
-        <v>-4.723633190104191</v>
+        <v>-5.547624664283251</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.799556919357873</v>
       </c>
       <c r="E20">
-        <v>-23.27683849437805</v>
+        <v>-21.61592102563678</v>
       </c>
       <c r="F20">
-        <v>3.011562645975958</v>
+        <v>1.896299519558429</v>
       </c>
       <c r="G20">
-        <v>-4.547436024867561</v>
+        <v>-4.400523945471324</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.281659415905966</v>
       </c>
       <c r="E21">
-        <v>-23.82045009968083</v>
+        <v>-21.54434849394555</v>
       </c>
       <c r="F21">
-        <v>3.370287872882147</v>
+        <v>2.463967819006291</v>
       </c>
       <c r="G21">
-        <v>-4.463546800902429</v>
+        <v>-4.481380709722483</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.752898607515367</v>
       </c>
       <c r="E22">
-        <v>-23.8804161524904</v>
+        <v>-23.70715673695693</v>
       </c>
       <c r="F22">
-        <v>3.336178014875412</v>
+        <v>2.429659997760127</v>
       </c>
       <c r="G22">
-        <v>-4.363376313975162</v>
+        <v>-3.573268273390543</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.230695868042705</v>
       </c>
       <c r="E23">
-        <v>-24.59800720069386</v>
+        <v>-23.89632921015335</v>
       </c>
       <c r="F23">
-        <v>3.810553366256567</v>
+        <v>2.3289077948317</v>
       </c>
       <c r="G23">
-        <v>-4.42665739195833</v>
+        <v>-4.129082385069861</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.732086577096592</v>
       </c>
       <c r="E24">
-        <v>-25.21959459993471</v>
+        <v>-23.99874517831082</v>
       </c>
       <c r="F24">
-        <v>3.972322590695045</v>
+        <v>2.592403201336599</v>
       </c>
       <c r="G24">
-        <v>-3.706484625890816</v>
+        <v>-3.945400076368939</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.280223685165811</v>
       </c>
       <c r="E25">
-        <v>-25.27822022443801</v>
+        <v>-22.61611602276292</v>
       </c>
       <c r="F25">
-        <v>3.840713461710196</v>
+        <v>2.914096632822068</v>
       </c>
       <c r="G25">
-        <v>-4.22561127190393</v>
+        <v>-3.223922955358951</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.889221475479209</v>
       </c>
       <c r="E26">
-        <v>-24.86391466595025</v>
+        <v>-24.63905781757339</v>
       </c>
       <c r="F26">
-        <v>3.791362017973272</v>
+        <v>2.621977325601516</v>
       </c>
       <c r="G26">
-        <v>-4.034119386275867</v>
+        <v>-3.060484632630672</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.568477092735737</v>
       </c>
       <c r="E27">
-        <v>-26.03097034483702</v>
+        <v>-23.86812134555957</v>
       </c>
       <c r="F27">
-        <v>3.865425608814713</v>
+        <v>3.036322304257939</v>
       </c>
       <c r="G27">
-        <v>-3.817096573448945</v>
+        <v>-2.868148557890094</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.324793000988213</v>
       </c>
       <c r="E28">
-        <v>-25.47948372323491</v>
+        <v>-25.40864027585891</v>
       </c>
       <c r="F28">
-        <v>3.636866754804408</v>
+        <v>2.959438133181099</v>
       </c>
       <c r="G28">
-        <v>-3.538921363420604</v>
+        <v>-4.485681108377997</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.156243322371637</v>
       </c>
       <c r="E29">
-        <v>-25.33538315183683</v>
+        <v>-24.87441619717404</v>
       </c>
       <c r="F29">
-        <v>4.088539681887738</v>
+        <v>2.504947793274202</v>
       </c>
       <c r="G29">
-        <v>-4.097509712261832</v>
+        <v>-3.738553880529736</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.059112115164414</v>
       </c>
       <c r="E30">
-        <v>-25.89465422025813</v>
+        <v>-24.27866827062096</v>
       </c>
       <c r="F30">
-        <v>3.697297805125746</v>
+        <v>2.612096584395089</v>
       </c>
       <c r="G30">
-        <v>-4.175251253160537</v>
+        <v>-3.255369827436488</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.024707872667147</v>
       </c>
       <c r="E31">
-        <v>-25.19481931863874</v>
+        <v>-24.66319911250828</v>
       </c>
       <c r="F31">
-        <v>3.817197012571836</v>
+        <v>2.809942629587277</v>
       </c>
       <c r="G31">
-        <v>-4.175903430631774</v>
+        <v>-4.923712630861124</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.038379114310013</v>
       </c>
       <c r="E32">
-        <v>-25.12130860007223</v>
+        <v>-23.39485052701794</v>
       </c>
       <c r="F32">
-        <v>3.87460160088877</v>
+        <v>2.58698217598805</v>
       </c>
       <c r="G32">
-        <v>-4.259342420403565</v>
+        <v>-4.003404144762509</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.087720957636837</v>
       </c>
       <c r="E33">
-        <v>-24.04715456545282</v>
+        <v>-23.27440217536192</v>
       </c>
       <c r="F33">
-        <v>3.836484966915973</v>
+        <v>2.379982310604622</v>
       </c>
       <c r="G33">
-        <v>-4.447983926322316</v>
+        <v>-4.096589380601914</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.158244126788982</v>
       </c>
       <c r="E34">
-        <v>-23.87847796561511</v>
+        <v>-23.36708645287692</v>
       </c>
       <c r="F34">
-        <v>3.796157479485223</v>
+        <v>2.645292644088615</v>
       </c>
       <c r="G34">
-        <v>-3.670293742055503</v>
+        <v>-3.472568099176992</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.239245582084772</v>
       </c>
       <c r="E35">
-        <v>-23.97646055771908</v>
+        <v>-22.25017003820307</v>
       </c>
       <c r="F35">
-        <v>3.953115405352595</v>
+        <v>2.376023045816023</v>
       </c>
       <c r="G35">
-        <v>-3.877126695712549</v>
+        <v>-3.828077653002707</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.324474417347077</v>
       </c>
       <c r="E36">
-        <v>-23.61914584461785</v>
+        <v>-22.5368767845767</v>
       </c>
       <c r="F36">
-        <v>4.10258240223994</v>
+        <v>2.498877448500323</v>
       </c>
       <c r="G36">
-        <v>-3.864990235765581</v>
+        <v>-4.239409625711613</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.408574900887048</v>
       </c>
       <c r="E37">
-        <v>-21.97388783899511</v>
+        <v>-21.36372577967561</v>
       </c>
       <c r="F37">
-        <v>3.703415661077089</v>
+        <v>2.113596640804045</v>
       </c>
       <c r="G37">
-        <v>-3.616580140680828</v>
+        <v>-4.422337130029582</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.48881568066671</v>
       </c>
       <c r="E38">
-        <v>-22.43612276638004</v>
+        <v>-21.87949179830522</v>
       </c>
       <c r="F38">
-        <v>3.660856732011485</v>
+        <v>2.526468772959109</v>
       </c>
       <c r="G38">
-        <v>-4.348780118692515</v>
+        <v>-3.778330085184079</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.562912730329599</v>
       </c>
       <c r="E39">
-        <v>-21.47596853642973</v>
+        <v>-20.15432886881712</v>
       </c>
       <c r="F39">
-        <v>3.630576274908282</v>
+        <v>2.364295703512194</v>
       </c>
       <c r="G39">
-        <v>-3.619910549493335</v>
+        <v>-3.402460676291846</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.630791998661492</v>
       </c>
       <c r="E40">
-        <v>-22.4619577105938</v>
+        <v>-20.69452147624411</v>
       </c>
       <c r="F40">
-        <v>3.760368893208122</v>
+        <v>2.258567496597457</v>
       </c>
       <c r="G40">
-        <v>-3.386374735516528</v>
+        <v>-3.859392103258673</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.695674880697952</v>
       </c>
       <c r="E41">
-        <v>-20.87253126101162</v>
+        <v>-19.12686792969081</v>
       </c>
       <c r="F41">
-        <v>3.652144765770652</v>
+        <v>2.514690752065986</v>
       </c>
       <c r="G41">
-        <v>-4.084274151195825</v>
+        <v>-3.376082249434933</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.760758367368332</v>
       </c>
       <c r="E42">
-        <v>-19.84457218974446</v>
+        <v>-19.57227504766324</v>
       </c>
       <c r="F42">
-        <v>3.748934536498649</v>
+        <v>2.86226035450382</v>
       </c>
       <c r="G42">
-        <v>-3.409743876478243</v>
+        <v>-3.478490665146748</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.834174085599246</v>
       </c>
       <c r="E43">
-        <v>-19.52453134620037</v>
+        <v>-19.49887301247291</v>
       </c>
       <c r="F43">
-        <v>3.414576208807412</v>
+        <v>2.37629861064531</v>
       </c>
       <c r="G43">
-        <v>-3.486733923539533</v>
+        <v>-3.479821504453535</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.9251598588558</v>
       </c>
       <c r="E44">
-        <v>-18.24397399478536</v>
+        <v>-18.62370918269855</v>
       </c>
       <c r="F44">
-        <v>4.020102998163853</v>
+        <v>2.350381263339143</v>
       </c>
       <c r="G44">
-        <v>-3.626594540937123</v>
+        <v>-3.45354570450834</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.0391009857443</v>
       </c>
       <c r="E45">
-        <v>-17.15148416890889</v>
+        <v>-18.31841757899745</v>
       </c>
       <c r="F45">
-        <v>3.689897147382898</v>
+        <v>2.543115105836293</v>
       </c>
       <c r="G45">
-        <v>-3.697913623489642</v>
+        <v>-3.824472468910441</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.183747265695419</v>
       </c>
       <c r="E46">
-        <v>-17.23515225467461</v>
+        <v>-16.75394302119753</v>
       </c>
       <c r="F46">
-        <v>3.588044268843241</v>
+        <v>2.283303399290705</v>
       </c>
       <c r="G46">
-        <v>-3.590205024369455</v>
+        <v>-4.577436188544437</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.362366245892199</v>
       </c>
       <c r="E47">
-        <v>-16.80513741985424</v>
+        <v>-15.91462659166789</v>
       </c>
       <c r="F47">
-        <v>3.625202760737196</v>
+        <v>2.348960679132994</v>
       </c>
       <c r="G47">
-        <v>-4.146654760792313</v>
+        <v>-3.860189944733638</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.577753611863951</v>
       </c>
       <c r="E48">
-        <v>-16.49706533311243</v>
+        <v>-15.69137735156375</v>
       </c>
       <c r="F48">
-        <v>3.391256139202566</v>
+        <v>2.484329525961096</v>
       </c>
       <c r="G48">
-        <v>-3.891789101905981</v>
+        <v>-2.547426216591041</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.834495601082343</v>
       </c>
       <c r="E49">
-        <v>-15.72096187225586</v>
+        <v>-16.17644031642135</v>
       </c>
       <c r="F49">
-        <v>3.49773185530939</v>
+        <v>2.540570090430182</v>
       </c>
       <c r="G49">
-        <v>-3.438734323765641</v>
+        <v>-4.220996371422187</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.131830558544265</v>
       </c>
       <c r="E50">
-        <v>-15.80861954362234</v>
+        <v>-14.29177094696109</v>
       </c>
       <c r="F50">
-        <v>3.791043693084269</v>
+        <v>2.058801999835755</v>
       </c>
       <c r="G50">
-        <v>-3.943089315582527</v>
+        <v>-3.881615795463801</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.471846374121198</v>
       </c>
       <c r="E51">
-        <v>-13.92230180962328</v>
+        <v>-13.98142556626742</v>
       </c>
       <c r="F51">
-        <v>3.787640309071989</v>
+        <v>2.284457920903061</v>
       </c>
       <c r="G51">
-        <v>-3.794922539426906</v>
+        <v>-3.540871274743235</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.855087509650274</v>
       </c>
       <c r="E52">
-        <v>-12.77327398576105</v>
+        <v>-15.19856163920502</v>
       </c>
       <c r="F52">
-        <v>2.945816678602405</v>
+        <v>2.686684381894541</v>
       </c>
       <c r="G52">
-        <v>-3.557367723165424</v>
+        <v>-4.265258365282242</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.274229155011624</v>
       </c>
       <c r="E53">
-        <v>-12.72346077167668</v>
+        <v>-13.10116267476043</v>
       </c>
       <c r="F53">
-        <v>3.588682502327162</v>
+        <v>1.954207726356473</v>
       </c>
       <c r="G53">
-        <v>-4.593687656596719</v>
+        <v>-4.497724873049865</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.727225640851429</v>
       </c>
       <c r="E54">
-        <v>-11.85478624515531</v>
+        <v>-12.34666909186846</v>
       </c>
       <c r="F54">
-        <v>3.589897204764305</v>
+        <v>2.108321316399716</v>
       </c>
       <c r="G54">
-        <v>-4.470045401796019</v>
+        <v>-4.391807279066422</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.205994786243498</v>
       </c>
       <c r="E55">
-        <v>-10.92301649028507</v>
+        <v>-11.19271428828589</v>
       </c>
       <c r="F55">
-        <v>3.613649626084066</v>
+        <v>2.181024503859795</v>
       </c>
       <c r="G55">
-        <v>-4.087078183267589</v>
+        <v>-3.858670404331112</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.698720228992272</v>
       </c>
       <c r="E56">
-        <v>-10.90628377882673</v>
+        <v>-11.96773091538062</v>
       </c>
       <c r="F56">
-        <v>3.248268083215284</v>
+        <v>1.904978227975038</v>
       </c>
       <c r="G56">
-        <v>-4.705027924173487</v>
+        <v>-3.704541335659263</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.197737700099823</v>
       </c>
       <c r="E57">
-        <v>-10.73088239508763</v>
+        <v>-10.46871544936157</v>
       </c>
       <c r="F57">
-        <v>3.597554422865454</v>
+        <v>1.991123911245366</v>
       </c>
       <c r="G57">
-        <v>-4.253621797711704</v>
+        <v>-4.219152397556813</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.68938419615972</v>
       </c>
       <c r="E58">
-        <v>-10.2563662461939</v>
+        <v>-11.48656243816961</v>
       </c>
       <c r="F58">
-        <v>3.552493238453456</v>
+        <v>2.087805989971113</v>
       </c>
       <c r="G58">
-        <v>-5.095010188699633</v>
+        <v>-5.022813811579208</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.16309112952942</v>
       </c>
       <c r="E59">
-        <v>-9.717663506715438</v>
+        <v>-10.7292113881788</v>
       </c>
       <c r="F59">
-        <v>3.57321286294515</v>
+        <v>1.946229015954489</v>
       </c>
       <c r="G59">
-        <v>-4.584106937806068</v>
+        <v>-5.367742861861411</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.611788076392605</v>
       </c>
       <c r="E60">
-        <v>-9.830934227069296</v>
+        <v>-9.491502457824364</v>
       </c>
       <c r="F60">
-        <v>3.230299355898708</v>
+        <v>1.849282458340863</v>
       </c>
       <c r="G60">
-        <v>-5.331800268941544</v>
+        <v>-5.789277935922351</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.02504902291742</v>
       </c>
       <c r="E61">
-        <v>-9.216809752993088</v>
+        <v>-9.111101584232038</v>
       </c>
       <c r="F61">
-        <v>3.525552817125915</v>
+        <v>2.056561055965409</v>
       </c>
       <c r="G61">
-        <v>-5.168103723661202</v>
+        <v>-4.370626408706165</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.400220269211</v>
       </c>
       <c r="E62">
-        <v>-9.30982008063663</v>
+        <v>-9.469077454538381</v>
       </c>
       <c r="F62">
-        <v>3.321869231929417</v>
+        <v>2.160684968787806</v>
       </c>
       <c r="G62">
-        <v>-5.533011916272907</v>
+        <v>-5.07067767898599</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.73610602255689</v>
       </c>
       <c r="E63">
-        <v>-8.654694802894975</v>
+        <v>-8.817122108602094</v>
       </c>
       <c r="F63">
-        <v>3.175861048761393</v>
+        <v>2.005703507902902</v>
       </c>
       <c r="G63">
-        <v>-5.531896262426173</v>
+        <v>-5.716042047502594</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.0281285015315</v>
       </c>
       <c r="E64">
-        <v>-7.239682529718218</v>
+        <v>-7.966932812980039</v>
       </c>
       <c r="F64">
-        <v>3.435808954015708</v>
+        <v>1.793510670822748</v>
       </c>
       <c r="G64">
-        <v>-5.101922607785632</v>
+        <v>-6.861669573549545</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.28095791592443</v>
       </c>
       <c r="E65">
-        <v>-7.550965304531471</v>
+        <v>-8.102189274641137</v>
       </c>
       <c r="F65">
-        <v>3.168111975717148</v>
+        <v>1.759708051763608</v>
       </c>
       <c r="G65">
-        <v>-5.244418419432481</v>
+        <v>-6.283323888929948</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.4959529359043</v>
       </c>
       <c r="E66">
-        <v>-7.433012142053681</v>
+        <v>-8.325895890620053</v>
       </c>
       <c r="F66">
-        <v>3.514026605473347</v>
+        <v>2.013081993762934</v>
       </c>
       <c r="G66">
-        <v>-5.942413840932418</v>
+        <v>-6.000272245322261</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.67258904299852</v>
       </c>
       <c r="E67">
-        <v>-7.479143706769818</v>
+        <v>-7.739472092048764</v>
       </c>
       <c r="F67">
-        <v>2.900280382415775</v>
+        <v>1.648196150845685</v>
       </c>
       <c r="G67">
-        <v>-6.114919747892761</v>
+        <v>-6.887554729121106</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.8122041963282</v>
       </c>
       <c r="E68">
-        <v>-7.244523468432417</v>
+        <v>-7.463112908782666</v>
       </c>
       <c r="F68">
-        <v>3.174183904196942</v>
+        <v>1.521914608560375</v>
       </c>
       <c r="G68">
-        <v>-5.880797967355503</v>
+        <v>-6.13949723797631</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.91165184232951</v>
       </c>
       <c r="E69">
-        <v>-7.66180423434321</v>
+        <v>-7.693666577461179</v>
       </c>
       <c r="F69">
-        <v>3.134219085420828</v>
+        <v>1.466850737586461</v>
       </c>
       <c r="G69">
-        <v>-6.114396681697556</v>
+        <v>-6.405151964775127</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.96699235818428</v>
       </c>
       <c r="E70">
-        <v>-6.422424297079941</v>
+        <v>-6.598160787895604</v>
       </c>
       <c r="F70">
-        <v>3.088912426591936</v>
+        <v>1.218858228287798</v>
       </c>
       <c r="G70">
-        <v>-6.212282892202727</v>
+        <v>-6.274011324327978</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.97609355957993</v>
       </c>
       <c r="E71">
-        <v>-6.81243912099055</v>
+        <v>-8.05689094914241</v>
       </c>
       <c r="F71">
-        <v>2.807147388646527</v>
+        <v>1.416167397174652</v>
       </c>
       <c r="G71">
-        <v>-6.533945428434933</v>
+        <v>-5.655459064133932</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.93479526663142</v>
       </c>
       <c r="E72">
-        <v>-7.494178240475284</v>
+        <v>-7.314588018279093</v>
       </c>
       <c r="F72">
-        <v>2.518124226490658</v>
+        <v>1.026471217386129</v>
       </c>
       <c r="G72">
-        <v>-6.184811985317855</v>
+        <v>-6.060653285413028</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.84165344977073</v>
       </c>
       <c r="E73">
-        <v>-6.991852732700442</v>
+        <v>-8.321530441676659</v>
       </c>
       <c r="F73">
-        <v>2.630844495022061</v>
+        <v>1.169338911723837</v>
       </c>
       <c r="G73">
-        <v>-5.6643247050881</v>
+        <v>-5.372993387086695</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.70192339215019</v>
       </c>
       <c r="E74">
-        <v>-6.728553668472465</v>
+        <v>-6.858620498920772</v>
       </c>
       <c r="F74">
-        <v>2.63804718952548</v>
+        <v>1.250231442472653</v>
       </c>
       <c r="G74">
-        <v>-5.664529958911534</v>
+        <v>-6.410336279089626</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.51838904963893</v>
       </c>
       <c r="E75">
-        <v>-8.035756560948613</v>
+        <v>-8.430548924937314</v>
       </c>
       <c r="F75">
-        <v>2.319117324862453</v>
+        <v>1.018197937683873</v>
       </c>
       <c r="G75">
-        <v>-5.490286015543074</v>
+        <v>-5.415341885625053</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.29869914990818</v>
       </c>
       <c r="E76">
-        <v>-8.318899398278202</v>
+        <v>-8.034316506214173</v>
       </c>
       <c r="F76">
-        <v>2.391666892848734</v>
+        <v>0.8859347381559479</v>
       </c>
       <c r="G76">
-        <v>-5.741506763790667</v>
+        <v>-5.361704426797781</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.0552706641537</v>
       </c>
       <c r="E77">
-        <v>-7.370410517371646</v>
+        <v>-7.994914253873434</v>
       </c>
       <c r="F77">
-        <v>2.186660913212844</v>
+        <v>0.9316721649938391</v>
       </c>
       <c r="G77">
-        <v>-5.973506484637253</v>
+        <v>-5.578859661446274</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.79737685657677</v>
       </c>
       <c r="E78">
-        <v>-8.192935365280844</v>
+        <v>-9.438229489598131</v>
       </c>
       <c r="F78">
-        <v>2.248059607848516</v>
+        <v>0.9077344500819718</v>
       </c>
       <c r="G78">
-        <v>-5.725847883389915</v>
+        <v>-5.844769300251615</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.53569314808494</v>
       </c>
       <c r="E79">
-        <v>-8.867972343234225</v>
+        <v>-10.3843046938586</v>
       </c>
       <c r="F79">
-        <v>2.009586754807559</v>
+        <v>0.9958043360395595</v>
       </c>
       <c r="G79">
-        <v>-4.632129711398736</v>
+        <v>-5.402222193652921</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.27997960847392</v>
       </c>
       <c r="E80">
-        <v>-9.639651484985301</v>
+        <v>-9.082024252628788</v>
       </c>
       <c r="F80">
-        <v>1.659883900501629</v>
+        <v>0.9576655301839467</v>
       </c>
       <c r="G80">
-        <v>-5.396577713508464</v>
+        <v>-4.949223694786748</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.03487570781018</v>
       </c>
       <c r="E81">
-        <v>-9.712011971153865</v>
+        <v>-9.921512764170718</v>
       </c>
       <c r="F81">
-        <v>1.977738428848072</v>
+        <v>0.2751809274255981</v>
       </c>
       <c r="G81">
-        <v>-4.73458778529364</v>
+        <v>-4.836870400274963</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.80672692619579</v>
       </c>
       <c r="E82">
-        <v>-11.20207011558573</v>
+        <v>-12.26315497421901</v>
       </c>
       <c r="F82">
-        <v>1.603535644030293</v>
+        <v>0.4687248354984953</v>
       </c>
       <c r="G82">
-        <v>-4.167587340237125</v>
+        <v>-4.957741728459292</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.595464111072793</v>
       </c>
       <c r="E83">
-        <v>-11.06900543534435</v>
+        <v>-12.48137760817463</v>
       </c>
       <c r="F83">
-        <v>1.651827588509788</v>
+        <v>0.3939850022311615</v>
       </c>
       <c r="G83">
-        <v>-4.867155270868215</v>
+        <v>-4.51369163418577</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.395567002917455</v>
       </c>
       <c r="E84">
-        <v>-12.67066329322125</v>
+        <v>-12.82808663514989</v>
       </c>
       <c r="F84">
-        <v>1.619915914313683</v>
+        <v>0.4587657008492543</v>
       </c>
       <c r="G84">
-        <v>-3.838439660540626</v>
+        <v>-3.780673951425883</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.20555934364954</v>
       </c>
       <c r="E85">
-        <v>-13.99123876944205</v>
+        <v>-14.10322340317773</v>
       </c>
       <c r="F85">
-        <v>1.527679298092574</v>
+        <v>0.1045548276550252</v>
       </c>
       <c r="G85">
-        <v>-3.549127775318178</v>
+        <v>-4.480980133712231</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.01704999329476</v>
       </c>
       <c r="E86">
-        <v>-14.96083939617236</v>
+        <v>-16.31168772113444</v>
       </c>
       <c r="F86">
-        <v>1.301861839021895</v>
+        <v>0.1295132410293932</v>
       </c>
       <c r="G86">
-        <v>-4.390436713213164</v>
+        <v>-3.438459548485881</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.823831223557233</v>
       </c>
       <c r="E87">
-        <v>-16.51243044542046</v>
+        <v>-16.3766667946705</v>
       </c>
       <c r="F87">
-        <v>1.199766653477175</v>
+        <v>0.02410494270957446</v>
       </c>
       <c r="G87">
-        <v>-2.931912975521997</v>
+        <v>-3.07552775156112</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.624854507047583</v>
       </c>
       <c r="E88">
-        <v>-17.11589489168261</v>
+        <v>-17.81875934241312</v>
       </c>
       <c r="F88">
-        <v>1.188403563533897</v>
+        <v>-0.01473227745474711</v>
       </c>
       <c r="G88">
-        <v>-3.333485459981131</v>
+        <v>-3.551008165184484</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.417201883240867</v>
       </c>
       <c r="E89">
-        <v>-19.46670273312242</v>
+        <v>-19.94437975687351</v>
       </c>
       <c r="F89">
-        <v>1.273408978545109</v>
+        <v>-0.2669540734005912</v>
       </c>
       <c r="G89">
-        <v>-2.698744632100048</v>
+        <v>-3.419437153817229</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.20244351209552</v>
       </c>
       <c r="E90">
-        <v>-20.48426442806797</v>
+        <v>-20.5932647974326</v>
       </c>
       <c r="F90">
-        <v>1.094841385461565</v>
+        <v>0.311799375602389</v>
       </c>
       <c r="G90">
-        <v>-2.935812798167258</v>
+        <v>-3.396634116142729</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.984111358968583</v>
       </c>
       <c r="E91">
-        <v>-22.18854203543269</v>
+        <v>-23.39297121030476</v>
       </c>
       <c r="F91">
-        <v>1.027858543768054</v>
+        <v>-0.2566956183333322</v>
       </c>
       <c r="G91">
-        <v>-2.427180581513633</v>
+        <v>-3.194283641145856</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.763644331817661</v>
       </c>
       <c r="E92">
-        <v>-24.38772751014768</v>
+        <v>-24.71797553410506</v>
       </c>
       <c r="F92">
-        <v>0.7526057045469317</v>
+        <v>-0.09539279528695133</v>
       </c>
       <c r="G92">
-        <v>-2.980296598578445</v>
+        <v>-3.881132455815067</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.547596705479747</v>
       </c>
       <c r="E93">
-        <v>-26.50331282620708</v>
+        <v>-26.57426495695925</v>
       </c>
       <c r="F93">
-        <v>0.6168631031227858</v>
+        <v>-0.5986842411251574</v>
       </c>
       <c r="G93">
-        <v>-2.489763134388016</v>
+        <v>-2.468780896760115</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.336606155994952</v>
       </c>
       <c r="E94">
-        <v>-27.87220259161571</v>
+        <v>-29.1415293274917</v>
       </c>
       <c r="F94">
-        <v>0.7037040332899924</v>
+        <v>-0.1548957939418422</v>
       </c>
       <c r="G94">
-        <v>-2.605407111165837</v>
+        <v>-3.212806143438078</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.128872206411389</v>
       </c>
       <c r="E95">
-        <v>-30.22354479298843</v>
+        <v>-31.48625769257622</v>
       </c>
       <c r="F95">
-        <v>0.7510267497492386</v>
+        <v>-0.08872222597112038</v>
       </c>
       <c r="G95">
-        <v>-3.106378725441588</v>
+        <v>-2.516717596168762</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.92166889758241</v>
       </c>
       <c r="E96">
-        <v>-33.6005999425205</v>
+        <v>-32.74709580392484</v>
       </c>
       <c r="F96">
-        <v>0.4893731932239948</v>
+        <v>-0.1062340541310921</v>
       </c>
       <c r="G96">
-        <v>-2.866910413858407</v>
+        <v>-2.889660482804278</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.710422242632065</v>
       </c>
       <c r="E97">
-        <v>-35.74998578857315</v>
+        <v>-35.42368432971345</v>
       </c>
       <c r="F97">
-        <v>0.5332014625808238</v>
+        <v>-0.6108954055861532</v>
       </c>
       <c r="G97">
-        <v>-2.258150747369525</v>
+        <v>-2.749962082138113</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.482200591226836</v>
       </c>
       <c r="E98">
-        <v>-38.45267417430497</v>
+        <v>-38.08018680904105</v>
       </c>
       <c r="F98">
-        <v>0.2468698086282448</v>
+        <v>-0.4184014945351924</v>
       </c>
       <c r="G98">
-        <v>-1.945075766266188</v>
+        <v>-3.471346507873001</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.241694938068743</v>
       </c>
       <c r="E99">
-        <v>-40.41403325108514</v>
+        <v>-39.71132050423388</v>
       </c>
       <c r="F99">
-        <v>0.1173844292760002</v>
+        <v>-0.1152516756136043</v>
       </c>
       <c r="G99">
-        <v>-2.657591240501368</v>
+        <v>-3.231709358467317</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.970529337867847</v>
       </c>
       <c r="E100">
-        <v>-42.45749356162437</v>
+        <v>-43.0407542211013</v>
       </c>
       <c r="F100">
-        <v>0.1457193036620851</v>
+        <v>-0.4931017351546403</v>
       </c>
       <c r="G100">
-        <v>-2.910533472429384</v>
+        <v>-3.067264629895099</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.690794733338338</v>
       </c>
       <c r="E101">
-        <v>-44.6719354652712</v>
+        <v>-45.58950845412739</v>
       </c>
       <c r="F101">
-        <v>0.1790230553578612</v>
+        <v>-0.5686278784089898</v>
       </c>
       <c r="G101">
-        <v>-3.156725502002824</v>
+        <v>-3.452572404119794</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.36692900566163</v>
       </c>
       <c r="E102">
-        <v>-48.16255115749362</v>
+        <v>-48.29319763261492</v>
       </c>
       <c r="F102">
-        <v>0.004889046984589923</v>
+        <v>-0.5386332802235244</v>
       </c>
       <c r="G102">
-        <v>-2.437469757049688</v>
+        <v>-3.440488912901454</v>
       </c>
     </row>
   </sheetData>
